--- a/artfynd/A 55797-2022 artfynd.xlsx
+++ b/artfynd/A 55797-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128936880</v>
       </c>
       <c r="B2" t="n">
-        <v>56656</v>
+        <v>56658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128936882</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55797-2022 artfynd.xlsx
+++ b/artfynd/A 55797-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128936880</v>
       </c>
       <c r="B2" t="n">
-        <v>56658</v>
+        <v>56660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128936882</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55797-2022 artfynd.xlsx
+++ b/artfynd/A 55797-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128936880</v>
+        <v>128936882</v>
       </c>
       <c r="B2" t="n">
-        <v>56660</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334136</v>
+        <v>334089</v>
       </c>
       <c r="R2" t="n">
-        <v>6619250</v>
+        <v>6619288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128936882</v>
+        <v>128936876</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334089</v>
+        <v>334110</v>
       </c>
       <c r="R3" t="n">
-        <v>6619288</v>
+        <v>6619329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128936880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Järnskogsfjället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619250</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 55797-2022 artfynd.xlsx
+++ b/artfynd/A 55797-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936876</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>